--- a/2026/ЗАВОДЫ/ПОКОМ/Симферополь/01,26/14,01,26 Симф КИ ПУД/дв 14,01,26пок.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/Симферополь/01,26/14,01,26 Симф КИ ПУД/дв 14,01,26пок.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\РАБОЧИЙ СТОЛ\14,01,26 Симф КИ ПУД\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\ПОКОМ_Останкино\2025_05\2026\ЗАВОДЫ\ПОКОМ\Симферополь\01,26\14,01,26 Симф КИ ПУД\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA43E042-9802-4FA5-A114-66B1CC2FD09B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0A6B9F-EA53-4CC5-83DC-A9ED10D9B391}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,10 @@
     <externalReference r:id="rId4"/>
     <externalReference r:id="rId5"/>
   </externalReferences>
-  <calcPr calcId="181029"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">TDSheet!$A$6:$AL$134</definedName>
+  </definedNames>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -32933,6 +32936,7 @@
       <c r="AO134" s="15"/>
     </row>
   </sheetData>
+  <autoFilter ref="A6:AL134" xr:uid="{32CCDCF2-8F7C-480E-BFC2-DF9FE7F9B53F}"/>
   <pageMargins left="0.75" right="1" top="0.75" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0" r:id="rId1"/>
 </worksheet>
